--- a/docs/all/01_TablasDescriptivas/idx10_juventud_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx10_juventud_summary_labels.xlsx
@@ -406,10 +406,10 @@
         <v>125</v>
       </c>
       <c r="D2">
-        <v>-2.565364028262495</v>
+        <v>-2.565364028262494</v>
       </c>
       <c r="E2">
-        <v>7.159583646361786</v>
+        <v>7.159583646361792</v>
       </c>
       <c r="F2">
         <v>-45.67405843675584</v>
@@ -463,7 +463,7 @@
         <v>-55.31968453630134</v>
       </c>
       <c r="E4">
-        <v>34.35299820172847</v>
+        <v>34.35299820172848</v>
       </c>
       <c r="F4">
         <v>-270.6974420709112</v>
@@ -490,7 +490,7 @@
         <v>-73.6261126184185</v>
       </c>
       <c r="E5">
-        <v>31.84773199569388</v>
+        <v>31.84773199569389</v>
       </c>
       <c r="F5">
         <v>-100</v>
@@ -541,10 +541,10 @@
         <v>125</v>
       </c>
       <c r="D7">
-        <v>82.33104000854493</v>
+        <v>82.33104000854492</v>
       </c>
       <c r="E7">
-        <v>17.64237138815768</v>
+        <v>17.64237138815767</v>
       </c>
       <c r="F7">
         <v>43.84000015258789</v>
@@ -652,7 +652,7 @@
         <v>-3.654400021076202</v>
       </c>
       <c r="E11">
-        <v>2.091984487810037</v>
+        <v>2.091984487810038</v>
       </c>
       <c r="F11">
         <v>-11.26000022888184</v>
@@ -679,7 +679,7 @@
         <v>-12.56488001251221</v>
       </c>
       <c r="E12">
-        <v>4.421421068910504</v>
+        <v>4.421421068910505</v>
       </c>
       <c r="F12">
         <v>-29.8799991607666</v>

--- a/docs/all/01_TablasDescriptivas/idx10_juventud_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx10_juventud_summary_labels.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -529,106 +529,106 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tcb_media</t>
+          <t>tcb_edsup</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cobertura bruta media</t>
+          <t>Cobertura bruta ed. superior</t>
         </is>
       </c>
       <c r="C7">
         <v>125</v>
       </c>
       <c r="D7">
-        <v>82.33104000854492</v>
+        <v>8.123331984642681</v>
       </c>
       <c r="E7">
-        <v>17.64237138815767</v>
+        <v>23.15077887745328</v>
       </c>
       <c r="F7">
-        <v>43.84000015258789</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>142.7100067138672</v>
+        <v>133.4175615919141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tcb_secundaria</t>
+          <t>tcb_media</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cobertura bruta secundaria</t>
+          <t>Cobertura bruta media</t>
         </is>
       </c>
       <c r="C8">
         <v>125</v>
       </c>
       <c r="D8">
-        <v>101.49872</v>
+        <v>82.33104000854492</v>
       </c>
       <c r="E8">
-        <v>17.08132185789212</v>
+        <v>17.64237138815767</v>
       </c>
       <c r="F8">
-        <v>63.62</v>
+        <v>43.84000015258789</v>
       </c>
       <c r="G8">
-        <v>145.41</v>
+        <v>142.7100067138672</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tdes_media</t>
+          <t>tcb_secundaria</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deserción intraanual (media)</t>
+          <t>Cobertura bruta secundaria</t>
         </is>
       </c>
       <c r="C9">
         <v>125</v>
       </c>
       <c r="D9">
-        <v>-3.484000003814697</v>
+        <v>101.49872</v>
       </c>
       <c r="E9">
-        <v>1.873912151184953</v>
+        <v>17.08132185789212</v>
       </c>
       <c r="F9">
-        <v>-13.32999992370605</v>
+        <v>63.62</v>
       </c>
       <c r="G9">
-        <v>-0</v>
+        <v>145.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tdes_secundaria</t>
+          <t>tdes_media</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deserción intraanual (secundaria)</t>
+          <t>Deserción intraanual (media)</t>
         </is>
       </c>
       <c r="C10">
         <v>125</v>
       </c>
       <c r="D10">
-        <v>-6.020559992790222</v>
+        <v>-3.484000003814697</v>
       </c>
       <c r="E10">
-        <v>2.738106595378933</v>
+        <v>1.873912151184953</v>
       </c>
       <c r="F10">
-        <v>-20.21999931335449</v>
+        <v>-13.32999992370605</v>
       </c>
       <c r="G10">
         <v>-0</v>
@@ -637,25 +637,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trep_media</t>
+          <t>tdes_secundaria</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Repitencia (media)</t>
+          <t>Deserción intraanual (secundaria)</t>
         </is>
       </c>
       <c r="C11">
         <v>125</v>
       </c>
       <c r="D11">
-        <v>-3.654400021076202</v>
+        <v>-6.020559992790222</v>
       </c>
       <c r="E11">
-        <v>2.091984487810038</v>
+        <v>2.738106595378933</v>
       </c>
       <c r="F11">
-        <v>-11.26000022888184</v>
+        <v>-20.21999931335449</v>
       </c>
       <c r="G11">
         <v>-0</v>
@@ -664,54 +664,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trep_secundaria</t>
+          <t>trep_media</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Repitencia (secundaria)</t>
+          <t>Repitencia (media)</t>
         </is>
       </c>
       <c r="C12">
         <v>125</v>
       </c>
       <c r="D12">
-        <v>-12.56488001251221</v>
+        <v>-3.654400021076202</v>
       </c>
       <c r="E12">
-        <v>4.421421068910505</v>
+        <v>2.091984487810038</v>
       </c>
       <c r="F12">
-        <v>-29.8799991607666</v>
+        <v>-11.26000022888184</v>
       </c>
       <c r="G12">
-        <v>-3.809999942779541</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>trep_secundaria</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Repitencia (secundaria)</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>125</v>
+      </c>
+      <c r="D13">
+        <v>-12.56488001251221</v>
+      </c>
+      <c r="E13">
+        <v>4.421421068910505</v>
+      </c>
+      <c r="F13">
+        <v>-29.8799991607666</v>
+      </c>
+      <c r="G13">
+        <v>-3.809999942779541</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>tti_edsup</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Tránsito inmediato a ed. sup.</t>
         </is>
       </c>
-      <c r="C13">
-        <v>125</v>
-      </c>
-      <c r="D13">
+      <c r="C14">
+        <v>125</v>
+      </c>
+      <c r="D14">
         <v>31.51521099388429</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>12.37999991810119</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>7.777777777777778</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>65.625</v>
       </c>
     </row>
